--- a/Test Data/Test execution.xlsx
+++ b/Test Data/Test execution.xlsx
@@ -26,10 +26,10 @@
     <t>Test Cases</t>
   </si>
   <si>
-    <t>C:\Users\Testing\API_Automation_UiPath\TC_03_Post_Orchestrator's_API.xaml</t>
+    <t>TC_03_Post_Orchestrator's_API.xaml</t>
   </si>
   <si>
-    <t>C:\Users\Testing\API_Automation_UiPath\TC_04_Get_Orchestrator'_API.xaml</t>
+    <t>TC_04_Get_Orchestrator'_API.xaml</t>
   </si>
 </sst>
 </file>
@@ -379,7 +379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="30">
+    <row r="2">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -387,7 +387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="30">
+    <row r="3">
       <c r="A3" t="b">
         <v>1</v>
       </c>
